--- a/content/xls/NSO_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_regions_01.07.2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6BF1E0-7204-4ED8-997D-A542C6B50613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E3337-4048-4342-AD37-2198EDAEC316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="4615" yWindow="7766" windowWidth="23631" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -365,9 +365,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1652,8 +1649,8 @@
       <c r="B24" s="4">
         <v>12495.999999999996</v>
       </c>
-      <c r="C24" s="11">
-        <v>0.318</v>
+      <c r="C24" s="5">
+        <v>0.31771428571428584</v>
       </c>
       <c r="D24" s="5">
         <v>3.7499999999999999E-2</v>

--- a/content/xls/NSO_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_regions_01.07.2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E3337-4048-4342-AD37-2198EDAEC316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A820E3A9-41DA-4983-8266-13F45E0AB616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4615" yWindow="7766" windowWidth="23631" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -231,12 +231,6 @@
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры (Уровень потребности в ДБО)</t>
-  </si>
-  <si>
-    <t>Изменение уровня потребности в ДБО с учетом альтернативной инфраструктуры</t>
-  </si>
-  <si>
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
@@ -253,6 +247,12 @@
   </si>
   <si>
     <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
@@ -687,7 +687,7 @@
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
@@ -707,34 +707,34 @@
         <v>62</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>31</v>

--- a/content/xls/NSO_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_regions_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A820E3A9-41DA-4983-8266-13F45E0AB616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACE8BEE-C39A-4DBE-9C25-754D71AC4B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="4702" yWindow="4702" windowWidth="23630" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -252,18 +252,20 @@
     <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_-\ #,##0.0_-;\-\ #,##0.0_-;_-\ &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,6 +285,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,9 +342,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -360,18 +368,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
+    <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -687,7 +714,7 @@
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
@@ -699,7 +726,7 @@
     <col min="13" max="13" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="103.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="118.15" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -745,19 +772,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>13847.999999999998</v>
+        <v>13848</v>
       </c>
       <c r="C2" s="5">
-        <v>0.21153846153846168</v>
-      </c>
-      <c r="D2" s="5">
+        <v>0.21199999999999997</v>
+      </c>
+      <c r="D2" s="9">
         <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>0.78846153846153832</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="F2" s="10">
-        <v>9.9999999999999978E-2</v>
+        <v>11.7</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -768,14 +795,14 @@
       <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" s="9">
-        <v>1</v>
+      <c r="J2" s="2">
+        <v>3</v>
       </c>
       <c r="K2" s="2">
         <v>12</v>
       </c>
       <c r="L2" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>32</v>
@@ -789,16 +816,16 @@
         <v>11175</v>
       </c>
       <c r="C3" s="5">
-        <v>0.24411764705882366</v>
-      </c>
-      <c r="D3" s="5">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="D3" s="9">
         <v>0</v>
       </c>
       <c r="E3" s="5">
-        <v>0.75588235294117634</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="F3" s="10">
-        <v>0.30000000000000004</v>
+        <v>9.2999999999999972</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -809,14 +836,14 @@
       <c r="I3" s="2">
         <v>4</v>
       </c>
-      <c r="J3" s="9">
-        <v>2</v>
+      <c r="J3" s="2">
+        <v>5</v>
       </c>
       <c r="K3" s="2">
         <v>21</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>33</v>
@@ -827,19 +854,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>9042.0000000000036</v>
+        <v>9042</v>
       </c>
       <c r="C4" s="5">
-        <v>0.1836000000000001</v>
-      </c>
-      <c r="D4" s="5">
+        <v>0.18400000000000005</v>
+      </c>
+      <c r="D4" s="9">
         <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>0.8163999999999999</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="F4" s="10">
-        <v>5.0000000000000044E-2</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -850,8 +877,8 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="9">
-        <v>3</v>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
       <c r="K4" s="2">
         <v>17</v>
@@ -871,16 +898,16 @@
         <v>14630</v>
       </c>
       <c r="C5" s="5">
-        <v>0.16653846153846164</v>
-      </c>
-      <c r="D5" s="5">
+        <v>0.16700000000000004</v>
+      </c>
+      <c r="D5" s="9">
         <v>0</v>
       </c>
       <c r="E5" s="5">
-        <v>0.83346153846153836</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="F5" s="10">
-        <v>0.18000000000000005</v>
+        <v>9.3999999999999968</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -891,14 +918,14 @@
       <c r="I5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="9">
-        <v>4</v>
+      <c r="J5" s="2">
+        <v>6</v>
       </c>
       <c r="K5" s="2">
         <v>17</v>
       </c>
       <c r="L5" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>35</v>
@@ -909,19 +936,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>12573.999999999998</v>
+        <v>12574</v>
       </c>
       <c r="C6" s="5">
-        <v>0.1306250000000001</v>
-      </c>
-      <c r="D6" s="5">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="D6" s="9">
         <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>0.8693749999999999</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="F6" s="10">
-        <v>0</v>
+        <v>-0.30000000000000027</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -932,14 +959,14 @@
       <c r="I6" s="2">
         <v>3</v>
       </c>
-      <c r="J6" s="9">
-        <v>1</v>
+      <c r="J6" s="2">
+        <v>6</v>
       </c>
       <c r="K6" s="2">
         <v>15</v>
       </c>
       <c r="L6" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>36</v>
@@ -950,19 +977,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>11776.000000000002</v>
+        <v>11776</v>
       </c>
       <c r="C7" s="5">
-        <v>0.12555555555555564</v>
-      </c>
-      <c r="D7" s="5">
+        <v>0.126</v>
+      </c>
+      <c r="D7" s="9">
         <v>0</v>
       </c>
       <c r="E7" s="5">
-        <v>0.87444444444444436</v>
+        <v>0.874</v>
       </c>
       <c r="F7" s="10">
-        <v>0.30000000000000004</v>
+        <v>4.0000000000000036</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -973,14 +1000,14 @@
       <c r="I7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="9">
-        <v>2</v>
+      <c r="J7" s="2">
+        <v>6</v>
       </c>
       <c r="K7" s="2">
         <v>16</v>
       </c>
       <c r="L7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>37</v>
@@ -991,19 +1018,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>57988.999999999993</v>
+        <v>57989</v>
       </c>
       <c r="C8" s="5">
-        <v>0.21160714285714288</v>
-      </c>
-      <c r="D8" s="5">
+        <v>0.21199999999999997</v>
+      </c>
+      <c r="D8" s="9">
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>0.78839285714285712</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="F8" s="10">
-        <v>-0.45</v>
+        <v>-0.30000000000000027</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -1014,14 +1041,14 @@
       <c r="I8" s="2">
         <v>17</v>
       </c>
-      <c r="J8" s="9">
-        <v>3</v>
+      <c r="J8" s="2">
+        <v>11</v>
       </c>
       <c r="K8" s="2">
         <v>22</v>
       </c>
       <c r="L8" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>38</v>
@@ -1035,16 +1062,16 @@
         <v>13325</v>
       </c>
       <c r="C9" s="5">
-        <v>0.18303030303030332</v>
-      </c>
-      <c r="D9" s="5">
+        <v>0.18300000000000005</v>
+      </c>
+      <c r="D9" s="9">
         <v>0</v>
       </c>
       <c r="E9" s="5">
-        <v>0.81696969696969668</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="F9" s="10">
-        <v>-0.05</v>
+        <v>0.8999999999999897</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1055,8 +1082,8 @@
       <c r="I9" s="2">
         <v>1</v>
       </c>
-      <c r="J9" s="9">
-        <v>4</v>
+      <c r="J9" s="2">
+        <v>7</v>
       </c>
       <c r="K9" s="2">
         <v>17</v>
@@ -1076,16 +1103,16 @@
         <v>5291</v>
       </c>
       <c r="C10" s="5">
-        <v>0.16529411764705904</v>
-      </c>
-      <c r="D10" s="5">
+        <v>0.16500000000000004</v>
+      </c>
+      <c r="D10" s="9">
         <v>0</v>
       </c>
       <c r="E10" s="5">
-        <v>0.83470588235294096</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="F10" s="10">
-        <v>-0.1</v>
+        <v>8.9999999999999964</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -1096,7 +1123,7 @@
       <c r="I10" s="2">
         <v>0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="2">
         <v>1</v>
       </c>
       <c r="K10" s="2">
@@ -1114,19 +1141,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>24203.000000000004</v>
+        <v>24203</v>
       </c>
       <c r="C11" s="5">
-        <v>0.15375000000000005</v>
-      </c>
-      <c r="D11" s="5">
+        <v>0.15400000000000003</v>
+      </c>
+      <c r="D11" s="9">
         <v>0</v>
       </c>
       <c r="E11" s="5">
-        <v>0.84624999999999995</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="F11" s="10">
-        <v>-0.37</v>
+        <v>1.0000000000000009</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -1137,14 +1164,14 @@
       <c r="I11" s="2">
         <v>8</v>
       </c>
-      <c r="J11" s="9">
-        <v>2</v>
+      <c r="J11" s="2">
+        <v>10</v>
       </c>
       <c r="K11" s="2">
         <v>16</v>
       </c>
       <c r="L11" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>41</v>
@@ -1155,19 +1182,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>44353.999999999993</v>
+        <v>44354</v>
       </c>
       <c r="C12" s="5">
-        <v>0.20540540540540553</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.18</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2.5</v>
       </c>
       <c r="E12" s="5">
-        <v>0.79459459459459447</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="F12" s="10">
-        <v>-0.45</v>
+        <v>-0.50000000000000044</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -1176,16 +1203,16 @@
         <v>6</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
-      </c>
-      <c r="J12" s="9">
-        <v>3</v>
+        <v>20</v>
+      </c>
+      <c r="J12" s="2">
+        <v>15</v>
       </c>
       <c r="K12" s="2">
         <v>19</v>
       </c>
       <c r="L12" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>42</v>
@@ -1199,16 +1226,16 @@
         <v>11524</v>
       </c>
       <c r="C13" s="5">
-        <v>0.11083333333333334</v>
-      </c>
-      <c r="D13" s="5">
+        <v>0.11099999999999999</v>
+      </c>
+      <c r="D13" s="9">
         <v>0</v>
       </c>
       <c r="E13" s="5">
-        <v>0.88916666666666666</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="F13" s="10">
-        <v>-0.05</v>
+        <v>5.8000000000000052</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
@@ -1219,14 +1246,14 @@
       <c r="I13" s="2">
         <v>2</v>
       </c>
-      <c r="J13" s="9">
-        <v>4</v>
+      <c r="J13" s="2">
+        <v>6</v>
       </c>
       <c r="K13" s="2">
         <v>10</v>
       </c>
       <c r="L13" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>43</v>
@@ -1237,19 +1264,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>27615.000000000004</v>
+        <v>27615</v>
       </c>
       <c r="C14" s="5">
-        <v>0.15709677419354862</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.6666666666666665E-2</v>
+        <v>0.13000000000000003</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2.7000000000000024</v>
       </c>
       <c r="E14" s="5">
-        <v>0.84290322580645138</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="F14" s="10">
-        <v>-0.37</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
@@ -1260,14 +1287,14 @@
       <c r="I14" s="2">
         <v>4</v>
       </c>
-      <c r="J14" s="9">
-        <v>1</v>
+      <c r="J14" s="2">
+        <v>14</v>
       </c>
       <c r="K14" s="2">
         <v>22</v>
       </c>
       <c r="L14" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>44</v>
@@ -1278,19 +1305,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>11205.000000000002</v>
+        <v>11205</v>
       </c>
       <c r="C15" s="5">
-        <v>0.1940740740740744</v>
-      </c>
-      <c r="D15" s="5">
-        <v>3.6249999999999998E-2</v>
+        <v>0.159</v>
+      </c>
+      <c r="D15" s="9">
+        <v>3.5</v>
       </c>
       <c r="E15" s="5">
-        <v>0.8059259259259256</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="F15" s="10">
-        <v>-0.1</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -1301,8 +1328,8 @@
       <c r="I15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="9">
-        <v>2</v>
+      <c r="J15" s="2">
+        <v>4</v>
       </c>
       <c r="K15" s="2">
         <v>20</v>
@@ -1322,16 +1349,16 @@
         <v>10013</v>
       </c>
       <c r="C16" s="5">
-        <v>0.163448275862069</v>
-      </c>
-      <c r="D16" s="5">
+        <v>0.16300000000000003</v>
+      </c>
+      <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="5">
-        <v>0.836551724137931</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="F16" s="10">
-        <v>9.9999999999999978E-2</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -1342,8 +1369,8 @@
       <c r="I16" s="2">
         <v>1</v>
       </c>
-      <c r="J16" s="9">
-        <v>3</v>
+      <c r="J16" s="2">
+        <v>2</v>
       </c>
       <c r="K16" s="2">
         <v>22</v>
@@ -1360,19 +1387,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>8394.9999999999982</v>
+        <v>8395</v>
       </c>
       <c r="C17" s="5">
-        <v>0.26000000000000012</v>
-      </c>
-      <c r="D17" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="D17" s="9">
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>0.73999999999999988</v>
+        <v>0.74</v>
       </c>
       <c r="F17" s="10">
-        <v>0.30000000000000004</v>
+        <v>6.7999999999999954</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -1383,14 +1410,14 @@
       <c r="I17" s="2">
         <v>1</v>
       </c>
-      <c r="J17" s="9">
-        <v>4</v>
+      <c r="J17" s="2">
+        <v>3</v>
       </c>
       <c r="K17" s="2">
         <v>16</v>
       </c>
       <c r="L17" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>47</v>
@@ -1404,16 +1431,16 @@
         <v>23573</v>
       </c>
       <c r="C18" s="5">
-        <v>0.15600000000000014</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.02</v>
+        <v>0.13600000000000004</v>
+      </c>
+      <c r="D18" s="9">
+        <v>2.0000000000000018</v>
       </c>
       <c r="E18" s="5">
-        <v>0.84399999999999986</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="F18" s="10">
-        <v>5.0000000000000044E-2</v>
+        <v>-0.10000000000000009</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -1424,14 +1451,14 @@
       <c r="I18" s="2">
         <v>2</v>
       </c>
-      <c r="J18" s="9">
-        <v>1</v>
+      <c r="J18" s="2">
+        <v>5</v>
       </c>
       <c r="K18" s="2">
         <v>21</v>
       </c>
       <c r="L18" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>48</v>
@@ -1445,16 +1472,16 @@
         <v>40472</v>
       </c>
       <c r="C19" s="5">
-        <v>0.17878787878787905</v>
-      </c>
-      <c r="D19" s="5">
+        <v>0.17900000000000005</v>
+      </c>
+      <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="5">
-        <v>0.82121212121212095</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="F19" s="10">
-        <v>0.18000000000000005</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -1465,14 +1492,14 @@
       <c r="I19" s="2">
         <v>13</v>
       </c>
-      <c r="J19" s="9">
-        <v>2</v>
+      <c r="J19" s="2">
+        <v>9</v>
       </c>
       <c r="K19" s="2">
         <v>27</v>
       </c>
       <c r="L19" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>49</v>
@@ -1483,19 +1510,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>181340</v>
+        <v>160478</v>
       </c>
       <c r="C20" s="5">
-        <v>0.15206349206349179</v>
-      </c>
-      <c r="D20" s="5">
+        <v>0.15500000000000003</v>
+      </c>
+      <c r="D20" s="9">
         <v>0</v>
       </c>
       <c r="E20" s="5">
-        <v>0.84793650793650821</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="F20" s="10">
-        <v>0</v>
+        <v>-0.30000000000000027</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -1506,14 +1533,14 @@
       <c r="I20" s="2">
         <v>72</v>
       </c>
-      <c r="J20" s="9">
-        <v>3</v>
+      <c r="J20" s="2">
+        <v>11</v>
       </c>
       <c r="K20" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L20" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>50</v>
@@ -1527,16 +1554,16 @@
         <v>33533</v>
       </c>
       <c r="C21" s="5">
-        <v>0.12176470588235322</v>
-      </c>
-      <c r="D21" s="5">
+        <v>0.122</v>
+      </c>
+      <c r="D21" s="9">
         <v>0</v>
       </c>
       <c r="E21" s="5">
-        <v>0.87823529411764678</v>
+        <v>0.878</v>
       </c>
       <c r="F21" s="10">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -1547,14 +1574,14 @@
       <c r="I21" s="2">
         <v>11</v>
       </c>
-      <c r="J21" s="9">
-        <v>4</v>
+      <c r="J21" s="2">
+        <v>23</v>
       </c>
       <c r="K21" s="2">
         <v>23</v>
       </c>
       <c r="L21" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>51</v>
@@ -1568,16 +1595,16 @@
         <v>7258</v>
       </c>
       <c r="C22" s="5">
-        <v>0.17307692307692324</v>
-      </c>
-      <c r="D22" s="5">
+        <v>0.17300000000000004</v>
+      </c>
+      <c r="D22" s="9">
         <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>0.82692307692307676</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="F22" s="10">
-        <v>-0.45</v>
+        <v>0.50000000000000044</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -1588,8 +1615,8 @@
       <c r="I22" s="2">
         <v>1</v>
       </c>
-      <c r="J22" s="9">
-        <v>1</v>
+      <c r="J22" s="2">
+        <v>2</v>
       </c>
       <c r="K22" s="2">
         <v>10</v>
@@ -1606,19 +1633,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>31325.000000000004</v>
+        <v>31325</v>
       </c>
       <c r="C23" s="5">
-        <v>0.16964285714285732</v>
-      </c>
-      <c r="D23" s="5">
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="D23" s="9">
         <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>0.83035714285714268</v>
+        <v>0.83</v>
       </c>
       <c r="F23" s="10">
-        <v>-0.05</v>
+        <v>10.499999999999998</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -1629,14 +1656,14 @@
       <c r="I23" s="2">
         <v>3</v>
       </c>
-      <c r="J23" s="9">
-        <v>2</v>
+      <c r="J23" s="2">
+        <v>13</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
       </c>
       <c r="L23" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>53</v>
@@ -1647,19 +1674,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>12495.999999999996</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0.31771428571428584</v>
-      </c>
-      <c r="D24" s="5">
-        <v>3.7499999999999999E-2</v>
+        <v>12496</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.28099999999999997</v>
+      </c>
+      <c r="D24" s="9">
+        <v>3.6999999999999922</v>
       </c>
       <c r="E24" s="5">
-        <v>0.68228571428571416</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="F24" s="10">
-        <v>-0.1</v>
+        <v>14.100000000000001</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -1668,10 +1695,10 @@
         <v>10</v>
       </c>
       <c r="I24" s="2">
-        <v>12</v>
-      </c>
-      <c r="J24" s="9">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>6</v>
       </c>
       <c r="K24" s="2">
         <v>8</v>
@@ -1691,16 +1718,16 @@
         <v>32597</v>
       </c>
       <c r="C25" s="5">
-        <v>0.22559322033898288</v>
-      </c>
-      <c r="D25" s="5">
+        <v>0.22599999999999998</v>
+      </c>
+      <c r="D25" s="9">
         <v>0</v>
       </c>
       <c r="E25" s="5">
-        <v>0.77440677966101712</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="F25" s="10">
-        <v>-0.37</v>
+        <v>-0.30000000000000027</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
@@ -1711,14 +1738,14 @@
       <c r="I25" s="2">
         <v>5</v>
       </c>
-      <c r="J25" s="9">
-        <v>4</v>
+      <c r="J25" s="2">
+        <v>11</v>
       </c>
       <c r="K25" s="2">
         <v>28</v>
       </c>
       <c r="L25" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>55</v>
@@ -1734,14 +1761,14 @@
       <c r="C26" s="5">
         <v>0.15000000000000002</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="9">
         <v>0</v>
       </c>
       <c r="E26" s="5">
         <v>0.85</v>
       </c>
       <c r="F26" s="10">
-        <v>-0.45</v>
+        <v>4.2999999999999927</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -1752,8 +1779,8 @@
       <c r="I26" s="2">
         <v>9</v>
       </c>
-      <c r="J26" s="9">
-        <v>1</v>
+      <c r="J26" s="2">
+        <v>3</v>
       </c>
       <c r="K26" s="2">
         <v>15</v>
@@ -1773,16 +1800,16 @@
         <v>10216</v>
       </c>
       <c r="C27" s="5">
-        <v>0.24333333333333351</v>
-      </c>
-      <c r="D27" s="5">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D27" s="9">
         <v>0</v>
       </c>
       <c r="E27" s="5">
-        <v>0.75666666666666649</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="F27" s="10">
-        <v>-0.05</v>
+        <v>-1.0000000000000009</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
@@ -1793,14 +1820,14 @@
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="9">
-        <v>2</v>
+      <c r="J27" s="2">
+        <v>5</v>
       </c>
       <c r="K27" s="2">
         <v>13</v>
       </c>
       <c r="L27" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>57</v>
@@ -1811,19 +1838,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>20330.000000000004</v>
+        <v>20330</v>
       </c>
       <c r="C28" s="5">
-        <v>0.18487804878048797</v>
-      </c>
-      <c r="D28" s="5">
+        <v>0.18500000000000005</v>
+      </c>
+      <c r="D28" s="9">
         <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>0.81512195121951203</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="F28" s="10">
-        <v>-0.37</v>
+        <v>10.7</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -1834,14 +1861,14 @@
       <c r="I28" s="2">
         <v>3</v>
       </c>
-      <c r="J28" s="9">
-        <v>3</v>
+      <c r="J28" s="2">
+        <v>10</v>
       </c>
       <c r="K28" s="2">
         <v>23</v>
       </c>
       <c r="L28" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>58</v>
@@ -1855,16 +1882,16 @@
         <v>29097</v>
       </c>
       <c r="C29" s="5">
-        <v>0.21538461538461562</v>
-      </c>
-      <c r="D29" s="5">
+        <v>0.21499999999999997</v>
+      </c>
+      <c r="D29" s="9">
         <v>0</v>
       </c>
       <c r="E29" s="5">
-        <v>0.78461538461538438</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="F29" s="10">
-        <v>-0.1</v>
+        <v>-0.10000000000000009</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -1875,14 +1902,14 @@
       <c r="I29" s="2">
         <v>0</v>
       </c>
-      <c r="J29" s="9">
-        <v>4</v>
+      <c r="J29" s="2">
+        <v>5</v>
       </c>
       <c r="K29" s="2">
         <v>19</v>
       </c>
       <c r="L29" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>59</v>
@@ -1896,16 +1923,16 @@
         <v>13816</v>
       </c>
       <c r="C30" s="5">
-        <v>0.20400000000000007</v>
-      </c>
-      <c r="D30" s="5">
+        <v>0.20399999999999996</v>
+      </c>
+      <c r="D30" s="9">
         <v>0</v>
       </c>
       <c r="E30" s="5">
-        <v>0.79599999999999993</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="F30" s="10">
-        <v>0.7</v>
+        <v>9.5000000000000089</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
@@ -1916,8 +1943,8 @@
       <c r="I30" s="2">
         <v>1</v>
       </c>
-      <c r="J30" s="9">
-        <v>1</v>
+      <c r="J30" s="2">
+        <v>6</v>
       </c>
       <c r="K30" s="2">
         <v>15</v>
@@ -1937,16 +1964,16 @@
         <v>7668</v>
       </c>
       <c r="C31" s="5">
-        <v>0.22705882352941198</v>
-      </c>
-      <c r="D31" s="5">
+        <v>0.22699999999999998</v>
+      </c>
+      <c r="D31" s="9">
         <v>0</v>
       </c>
       <c r="E31" s="5">
-        <v>0.77294117647058802</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="F31" s="10">
-        <v>0.9</v>
+        <v>-5.8999999999999941</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
@@ -1957,7 +1984,7 @@
       <c r="I31" s="2">
         <v>0</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="2">
         <v>2</v>
       </c>
       <c r="K31" s="2">
@@ -1977,6 +2004,19 @@
       <c r="J33" s="8"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D31">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F31">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/content/xls/NSO_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_regions_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACE8BEE-C39A-4DBE-9C25-754D71AC4B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91804F07-A1EE-47C4-82D7-18FC5A398F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4702" yWindow="4702" windowWidth="23630" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1188,7 +1188,7 @@
         <v>0.18</v>
       </c>
       <c r="D12" s="9">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E12" s="5">
         <v>0.79500000000000004</v>
@@ -1270,7 +1270,7 @@
         <v>0.13000000000000003</v>
       </c>
       <c r="D14" s="9">
-        <v>2.7000000000000024</v>
+        <v>-2.7</v>
       </c>
       <c r="E14" s="5">
         <v>0.84299999999999997</v>
@@ -1311,7 +1311,7 @@
         <v>0.159</v>
       </c>
       <c r="D15" s="9">
-        <v>3.5</v>
+        <v>-3.5</v>
       </c>
       <c r="E15" s="5">
         <v>0.80600000000000005</v>
@@ -1434,7 +1434,7 @@
         <v>0.13600000000000004</v>
       </c>
       <c r="D18" s="9">
-        <v>2.0000000000000018</v>
+        <v>-2</v>
       </c>
       <c r="E18" s="5">
         <v>0.84399999999999997</v>
@@ -1680,7 +1680,7 @@
         <v>0.28099999999999997</v>
       </c>
       <c r="D24" s="9">
-        <v>3.6999999999999922</v>
+        <v>-3.7</v>
       </c>
       <c r="E24" s="5">
         <v>0.68200000000000005</v>

--- a/content/xls/NSO_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_regions_01.07.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91804F07-A1EE-47C4-82D7-18FC5A398F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF6DC37-B02E-41E6-82B1-D20A8B7EC916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -234,9 +234,6 @@
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников</t>
-  </si>
-  <si>
     <t>Количество торговых точек с сервисом "Выдача наличных на кассе"</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
   </si>
 </sst>
 </file>
@@ -734,10 +734,10 @@
         <v>62</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>64</v>
@@ -749,19 +749,19 @@
         <v>63</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>31</v>
